--- a/data/pupil/3_processed/15_semantic_similarity/mean/sub_1031_cosine_similarity_story_avg.xlsx
+++ b/data/pupil/3_processed/15_semantic_similarity/mean/sub_1031_cosine_similarity_story_avg.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,10 +446,15 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Grandfather Clocks</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Impatient Billionaire</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Dont Look</t>
         </is>
@@ -469,9 +474,12 @@
         <v>0.08377967832126609</v>
       </c>
       <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.2015373517447812</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.089911838034439</v>
       </c>
     </row>
